--- a/featsextra_passives.xlsx
+++ b/featsextra_passives.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/99bdd68f8c92d318/Documents/Projects/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tyler\GitHub\zz_CXUtils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{50AE4EE7-CD8F-445D-A500-51465F5649A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92F93ACB-3268-4D1C-88A6-EAC73C907D82}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B452FB95-81E5-48E1-AACA-7BBCC30E8CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5385" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2131,7 +2131,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>57</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>96</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>425</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>425</v>
       </c>
@@ -5288,7 +5288,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>425</v>
       </c>
